--- a/docs/01_設計/03_画面設計書.xlsx
+++ b/docs/01_設計/03_画面設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2630b65481ecdb8/個人開発/仕様書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Documents/projects/task-manager-app/docs/01_設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{1B5F0858-70DD-BE4B-977C-C984D8A7AD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6615D4B2-5CC7-48E6-B396-56E67E06D7BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8984A05F-7592-CD47-8B2B-E4627E7FE78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C44B622-FDC5-B543-A5EF-6C0AFF8FD1C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" activeTab="1" xr2:uid="{6C44B622-FDC5-B543-A5EF-6C0AFF8FD1C5}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="タスク作成画面" sheetId="6" r:id="rId8"/>
     <sheet name="タスク編集画面" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="506">
   <si>
     <t>■ 画面仕様書一覧（MVP）</t>
   </si>
@@ -1591,6 +1591,15 @@
   <si>
     <t>添付ファイル（将来）</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基本画面遷移図</t>
+  </si>
+  <si>
+    <t>認証ガード補足図</t>
+  </si>
+  <si>
+    <t>未認証アクセス</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1696,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1732,13 +1741,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1778,6 +1802,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1801,21 +1833,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>33867</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>128337</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>135467</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>64234</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDE02BBE-1429-4B4A-A8EC-02CB1B1D2E9D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E724CA9-1489-FD45-9FC2-C8EE32A3E907}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1823,21 +1855,86 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="3595" t="16123" r="7353" b="14334"/>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="347133" y="287867"/>
-          <a:ext cx="8112404" cy="3911600"/>
+          <a:off x="347133" y="254000"/>
+          <a:ext cx="6028267" cy="4382234"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>316732</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A052A776-9F5A-A87B-1982-E0E00F0ED047}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6773333" y="254001"/>
+          <a:ext cx="4719399" cy="3905250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2550,9 +2647,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E99835-E7DD-2742-9C1D-E16B895CE598}">
   <dimension ref="B2:C10"/>
-  <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.5703125" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:3" ht="39.75">
+    <row r="2" spans="2:3" ht="40">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2605,93 +2702,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A202628C-125D-9142-AC8E-7C60C80478FE}">
-  <dimension ref="B19:N34"/>
-  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="19.5"/>
+  <dimension ref="B2:U40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.85546875" defaultRowHeight="20"/>
   <sheetData>
-    <row r="19" spans="2:14">
-      <c r="B19" t="s">
+    <row r="2" spans="2:21">
+      <c r="B2" t="s">
+        <v>503</v>
+      </c>
+      <c r="U2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="10" t="s">
+    <row r="22" spans="2:14">
+      <c r="B22" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="10" t="s">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="10" t="s">
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="7"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="8" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="7"/>
       <c r="F23" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="7"/>
       <c r="K23" s="6" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -2699,20 +2762,20 @@
     </row>
     <row r="24" spans="2:14">
       <c r="B24" s="8" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
       <c r="F24" s="8" t="s">
-        <v>496</v>
+        <v>50</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="7"/>
       <c r="K24" s="6" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -2720,20 +2783,20 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="7"/>
       <c r="F25" s="8" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="7"/>
       <c r="K25" s="6" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -2741,20 +2804,20 @@
     </row>
     <row r="26" spans="2:14">
       <c r="B26" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="7"/>
       <c r="F26" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="7"/>
       <c r="K26" s="6" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -2768,14 +2831,14 @@
       <c r="D27" s="6"/>
       <c r="E27" s="7"/>
       <c r="F27" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="7"/>
       <c r="K27" s="6" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -2783,20 +2846,20 @@
     </row>
     <row r="28" spans="2:14">
       <c r="B28" s="8" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="7"/>
       <c r="F28" s="8" t="s">
-        <v>76</v>
+        <v>497</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="7"/>
       <c r="K28" s="6" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -2804,20 +2867,20 @@
     </row>
     <row r="29" spans="2:14">
       <c r="B29" s="8" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="7"/>
       <c r="F29" s="8" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="7"/>
       <c r="K29" s="6" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -2825,20 +2888,20 @@
     </row>
     <row r="30" spans="2:14">
       <c r="B30" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="7"/>
       <c r="K30" s="6" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -2846,13 +2909,13 @@
     </row>
     <row r="31" spans="2:14">
       <c r="B31" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
       <c r="F31" s="8" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -2873,14 +2936,14 @@
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
       <c r="F32" s="8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="7"/>
       <c r="K32" s="6" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
@@ -2888,20 +2951,20 @@
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="8" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
       <c r="F33" s="8" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="7"/>
       <c r="K33" s="6" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -2909,30 +2972,168 @@
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="8" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
       <c r="F34" s="8" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="7"/>
       <c r="K34" s="6" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
       <c r="N34" s="7"/>
     </row>
+    <row r="35" spans="2:14">
+      <c r="B35" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="7"/>
+    </row>
+    <row r="37" spans="2:14" ht="18" customHeight="1">
+      <c r="B37" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="15"/>
+    </row>
+    <row r="38" spans="2:14" ht="18" customHeight="1">
+      <c r="B38" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="15"/>
+    </row>
+    <row r="39" spans="2:14" ht="18" customHeight="1">
+      <c r="B39" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="2:14" ht="18" customHeight="1">
+      <c r="B40" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:N20"/>
+  <mergeCells count="15">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="K37:N37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2943,14 +3144,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6085C9-D4CF-764D-8E83-788B760B2E2B}">
   <dimension ref="B2:K307"/>
-  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.85546875" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:5" ht="39.75">
+    <row r="2" spans="2:5" ht="40">
       <c r="B2" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="30">
+    <row r="4" spans="2:5" ht="31">
       <c r="B4" s="2" t="s">
         <v>267</v>
       </c>
@@ -2960,7 +3161,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="30">
+    <row r="7" spans="2:5" ht="31">
       <c r="B7" s="2" t="s">
         <v>269</v>
       </c>
@@ -2970,7 +3171,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="22.5">
+    <row r="10" spans="2:5" ht="24">
       <c r="C10" s="5" t="s">
         <v>271</v>
       </c>
@@ -3020,7 +3221,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="22" spans="3:5" ht="22.5">
+    <row r="22" spans="3:5" ht="24">
       <c r="C22" s="5" t="s">
         <v>279</v>
       </c>
@@ -3105,12 +3306,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="39.75">
+    <row r="41" spans="2:6" ht="40">
       <c r="B41" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="30">
+    <row r="43" spans="2:6" ht="31">
       <c r="C43" s="2" t="s">
         <v>295</v>
       </c>
@@ -3120,7 +3321,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="22.5">
+    <row r="45" spans="2:6" ht="24">
       <c r="D45" s="5" t="s">
         <v>297</v>
       </c>
@@ -3140,7 +3341,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="4:6" ht="22.5">
+    <row r="50" spans="4:6" ht="24">
       <c r="D50" s="5" t="s">
         <v>301</v>
       </c>
@@ -3185,7 +3386,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="60" spans="4:6" ht="22.5">
+    <row r="60" spans="4:6" ht="24">
       <c r="D60" s="5" t="s">
         <v>309</v>
       </c>
@@ -3205,7 +3406,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="65" spans="3:4" ht="30">
+    <row r="65" spans="3:4" ht="31">
       <c r="C65" s="2" t="s">
         <v>312</v>
       </c>
@@ -3255,7 +3456,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="77" spans="3:4" ht="30">
+    <row r="77" spans="3:4" ht="31">
       <c r="C77" s="2" t="s">
         <v>320</v>
       </c>
@@ -3280,12 +3481,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="83" spans="2:4" ht="39.75">
+    <row r="83" spans="2:4" ht="40">
       <c r="B83" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="84" spans="2:4" ht="30">
+    <row r="84" spans="2:4" ht="31">
       <c r="C84" s="2" t="s">
         <v>326</v>
       </c>
@@ -3295,27 +3496,27 @@
         <v>327</v>
       </c>
     </row>
-    <row r="86" spans="2:4" ht="22.5">
+    <row r="86" spans="2:4" ht="24">
       <c r="D86" s="5" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="88" spans="2:4" ht="22.5">
+    <row r="88" spans="2:4" ht="24">
       <c r="D88" s="5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="90" spans="2:4" ht="22.5">
+    <row r="90" spans="2:4" ht="24">
       <c r="D90" s="5" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="92" spans="2:4" ht="22.5">
+    <row r="92" spans="2:4" ht="24">
       <c r="D92" s="5" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="94" spans="2:4" ht="30">
+    <row r="94" spans="2:4" ht="31">
       <c r="C94" s="2" t="s">
         <v>332</v>
       </c>
@@ -3370,12 +3571,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="109" spans="2:4" ht="39.75">
+    <row r="109" spans="2:4" ht="40">
       <c r="B109" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="110" spans="2:4" ht="30">
+    <row r="110" spans="2:4" ht="31">
       <c r="C110" s="2" t="s">
         <v>342</v>
       </c>
@@ -3385,7 +3586,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="113" spans="3:8" ht="30">
+    <row r="113" spans="3:8" ht="31">
       <c r="C113" s="2" t="s">
         <v>344</v>
       </c>
@@ -3438,7 +3639,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="123" spans="3:8" ht="30">
+    <row r="123" spans="3:8" ht="31">
       <c r="C123" s="2" t="s">
         <v>354</v>
       </c>
@@ -3463,7 +3664,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" spans="2:4" ht="30">
+    <row r="130" spans="2:4" ht="31">
       <c r="C130" s="2" t="s">
         <v>356</v>
       </c>
@@ -3488,7 +3689,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="136" spans="2:4" ht="30">
+    <row r="136" spans="2:4" ht="31">
       <c r="C136" s="2" t="s">
         <v>361</v>
       </c>
@@ -3508,12 +3709,12 @@
         <v>364</v>
       </c>
     </row>
-    <row r="141" spans="2:4" ht="39.75">
+    <row r="141" spans="2:4" ht="40">
       <c r="B141" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="142" spans="2:4" ht="30">
+    <row r="142" spans="2:4" ht="31">
       <c r="C142" s="2" t="s">
         <v>366</v>
       </c>
@@ -3528,7 +3729,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="147" spans="3:11" ht="30">
+    <row r="147" spans="3:11" ht="31">
       <c r="C147" s="2" t="s">
         <v>369</v>
       </c>
@@ -3610,7 +3811,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="156" spans="3:11" ht="30">
+    <row r="156" spans="3:11" ht="31">
       <c r="C156" s="2" t="s">
         <v>378</v>
       </c>
@@ -3645,7 +3846,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="164" spans="2:5" ht="30">
+    <row r="164" spans="2:5" ht="31">
       <c r="C164" s="2" t="s">
         <v>382</v>
       </c>
@@ -3670,7 +3871,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="170" spans="2:5" ht="30">
+    <row r="170" spans="2:5" ht="31">
       <c r="C170" s="2" t="s">
         <v>387</v>
       </c>
@@ -3690,12 +3891,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="175" spans="2:5" ht="39.75">
+    <row r="175" spans="2:5" ht="40">
       <c r="B175" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="177" spans="3:5" ht="30">
+    <row r="177" spans="3:5" ht="31">
       <c r="C177" s="2" t="s">
         <v>392</v>
       </c>
@@ -3705,7 +3906,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="180" spans="3:5" ht="22.5">
+    <row r="180" spans="3:5" ht="24">
       <c r="D180" s="5" t="s">
         <v>394</v>
       </c>
@@ -3725,7 +3926,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="185" spans="3:5" ht="22.5">
+    <row r="185" spans="3:5" ht="24">
       <c r="D185" s="5" t="s">
         <v>397</v>
       </c>
@@ -3755,12 +3956,12 @@
         <v>401</v>
       </c>
     </row>
-    <row r="192" spans="3:5" ht="30">
+    <row r="192" spans="3:5" ht="31">
       <c r="C192" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="193" spans="3:5" ht="22.5">
+    <row r="193" spans="3:5" ht="24">
       <c r="D193" s="5" t="s">
         <v>49</v>
       </c>
@@ -3775,7 +3976,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="196" spans="3:5" ht="22.5">
+    <row r="196" spans="3:5" ht="24">
       <c r="D196" s="5" t="s">
         <v>98</v>
       </c>
@@ -3790,7 +3991,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="199" spans="3:5" ht="22.5">
+    <row r="199" spans="3:5" ht="24">
       <c r="D199" s="5" t="s">
         <v>97</v>
       </c>
@@ -3805,7 +4006,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="203" spans="3:5" ht="30">
+    <row r="203" spans="3:5" ht="31">
       <c r="C203" s="2" t="s">
         <v>409</v>
       </c>
@@ -3830,12 +4031,12 @@
         <v>413</v>
       </c>
     </row>
-    <row r="209" spans="2:9" ht="39.75">
+    <row r="209" spans="2:9" ht="40">
       <c r="B209" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="210" spans="2:9" ht="30">
+    <row r="210" spans="2:9" ht="31">
       <c r="C210" s="2" t="s">
         <v>415</v>
       </c>
@@ -3845,7 +4046,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="213" spans="2:9" ht="30">
+    <row r="213" spans="2:9" ht="31">
       <c r="C213" s="2" t="s">
         <v>417</v>
       </c>
@@ -3865,7 +4066,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="218" spans="2:9" ht="30">
+    <row r="218" spans="2:9" ht="31">
       <c r="C218" s="2" t="s">
         <v>421</v>
       </c>
@@ -3875,12 +4076,12 @@
         <v>422</v>
       </c>
     </row>
-    <row r="221" spans="2:9" ht="39.75">
+    <row r="221" spans="2:9" ht="40">
       <c r="B221" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="222" spans="2:9" ht="30">
+    <row r="222" spans="2:9" ht="31">
       <c r="C222" s="2" t="s">
         <v>424</v>
       </c>
@@ -3917,7 +4118,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="228" spans="3:9" ht="30">
+    <row r="228" spans="3:9" ht="31">
       <c r="C228" s="2" t="s">
         <v>433</v>
       </c>
@@ -3937,7 +4138,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="233" spans="3:9" ht="30">
+    <row r="233" spans="3:9" ht="31">
       <c r="C233" s="2" t="s">
         <v>437</v>
       </c>
@@ -3957,7 +4158,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="238" spans="3:9" ht="30">
+    <row r="238" spans="3:9" ht="31">
       <c r="C238" s="2" t="s">
         <v>441</v>
       </c>
@@ -3982,12 +4183,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="244" spans="2:4" ht="39.75">
+    <row r="244" spans="2:4" ht="40">
       <c r="B244" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="245" spans="2:4" ht="30">
+    <row r="245" spans="2:4" ht="31">
       <c r="C245" s="2" t="s">
         <v>447</v>
       </c>
@@ -4007,7 +4208,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="250" spans="2:4" ht="30">
+    <row r="250" spans="2:4" ht="31">
       <c r="C250" s="2" t="s">
         <v>451</v>
       </c>
@@ -4027,7 +4228,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="255" spans="2:4" ht="39.75">
+    <row r="255" spans="2:4" ht="40">
       <c r="B255" s="1" t="s">
         <v>455</v>
       </c>
@@ -4037,7 +4238,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="258" spans="2:4" ht="30">
+    <row r="258" spans="2:4" ht="31">
       <c r="C258" s="2" t="s">
         <v>457</v>
       </c>
@@ -4057,7 +4258,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="263" spans="2:4" ht="30">
+    <row r="263" spans="2:4" ht="31">
       <c r="C263" s="2" t="s">
         <v>460</v>
       </c>
@@ -4082,7 +4283,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="269" spans="2:4" ht="39.75">
+    <row r="269" spans="2:4" ht="40">
       <c r="B269" s="1" t="s">
         <v>464</v>
       </c>
@@ -4132,7 +4333,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="282" spans="3:4" ht="22.5">
+    <row r="282" spans="3:4" ht="24">
       <c r="C282" s="5" t="s">
         <v>474</v>
       </c>
@@ -4152,7 +4353,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="286" spans="3:4" ht="22.5">
+    <row r="286" spans="3:4" ht="24">
       <c r="C286" s="5" t="s">
         <v>478</v>
       </c>
@@ -4162,7 +4363,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="288" spans="3:4" ht="22.5">
+    <row r="288" spans="3:4" ht="24">
       <c r="C288" s="5" t="s">
         <v>480</v>
       </c>
@@ -4182,7 +4383,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="292" spans="2:4" ht="22.5">
+    <row r="292" spans="2:4" ht="24">
       <c r="C292" s="5" t="s">
         <v>481</v>
       </c>
@@ -4202,7 +4403,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="296" spans="2:4" ht="22.5">
+    <row r="296" spans="2:4" ht="24">
       <c r="C296" s="5" t="s">
         <v>483</v>
       </c>
@@ -4217,7 +4418,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="300" spans="2:4" ht="39.75">
+    <row r="300" spans="2:4" ht="40">
       <c r="B300" s="1" t="s">
         <v>485</v>
       </c>
@@ -4227,7 +4428,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="302" spans="2:4" ht="30">
+    <row r="302" spans="2:4" ht="31">
       <c r="C302" s="2" t="s">
         <v>487</v>
       </c>
@@ -4267,20 +4468,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F61217D-9301-984A-8712-4F086D9AC4AA}">
   <dimension ref="B2:F49"/>
-  <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.5703125" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="39.75">
+    <row r="2" spans="2:3" ht="40">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="30">
+    <row r="4" spans="2:3" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -4325,7 +4526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30">
+    <row r="17" spans="2:6" ht="31">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
@@ -4360,7 +4561,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="30">
+    <row r="25" spans="2:6" ht="31">
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
@@ -4407,7 +4608,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="30">
+    <row r="30" spans="2:6" ht="31">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -4436,7 +4637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="2:4" ht="30">
+    <row r="36" spans="2:4" ht="31">
       <c r="B36" s="2" t="s">
         <v>40</v>
       </c>
@@ -4461,7 +4662,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="2:4" ht="30">
+    <row r="42" spans="2:4" ht="31">
       <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
@@ -4490,7 +4691,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="2:4" ht="30">
+    <row r="48" spans="2:4" ht="31">
       <c r="B48" s="2" t="s">
         <v>52</v>
       </c>
@@ -4510,14 +4711,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C869CE67-ABD4-1848-BA84-4E0693E06711}">
   <dimension ref="B2:K53"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.7109375" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:3" ht="39.75">
+    <row r="2" spans="2:3" ht="40">
       <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="30">
+    <row r="4" spans="2:3" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -4562,7 +4763,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="30">
+    <row r="17" spans="2:11" ht="31">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
@@ -4607,7 +4808,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="30">
+    <row r="27" spans="2:11" ht="31">
       <c r="B27" s="2" t="s">
         <v>24</v>
       </c>
@@ -4682,7 +4883,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="30">
+    <row r="34" spans="2:8" ht="31">
       <c r="B34" s="2" t="s">
         <v>34</v>
       </c>
@@ -4711,7 +4912,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="30">
+    <row r="39" spans="2:8" ht="31">
       <c r="B39" s="2" t="s">
         <v>40</v>
       </c>
@@ -4746,7 +4947,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="30">
+    <row r="47" spans="2:8" ht="31">
       <c r="B47" s="2" t="s">
         <v>45</v>
       </c>
@@ -4775,7 +4976,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="30">
+    <row r="52" spans="2:8" ht="31">
       <c r="B52" s="2" t="s">
         <v>52</v>
       </c>
@@ -4795,14 +4996,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517F20CB-A3F3-CD45-950B-08A0749A7C13}">
   <dimension ref="B2:O129"/>
-  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.85546875" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="39.75">
+    <row r="2" spans="2:7" ht="40">
       <c r="B2" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="30">
+    <row r="4" spans="2:7" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -4863,7 +5064,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="30">
+    <row r="13" spans="2:7" ht="31">
       <c r="B13" s="2" t="s">
         <v>164</v>
       </c>
@@ -4888,12 +5089,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="30">
+    <row r="20" spans="2:4" ht="31">
       <c r="B20" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="22.5">
+    <row r="21" spans="2:4" ht="24">
       <c r="C21" s="5" t="s">
         <v>170</v>
       </c>
@@ -4913,7 +5114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="22.5">
+    <row r="26" spans="2:4" ht="24">
       <c r="C26" s="5" t="s">
         <v>171</v>
       </c>
@@ -4923,7 +5124,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="22.5">
+    <row r="29" spans="2:4" ht="24">
       <c r="C29" s="5" t="s">
         <v>172</v>
       </c>
@@ -4938,7 +5139,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="2:15" ht="30">
+    <row r="33" spans="2:15" ht="31">
       <c r="B33" s="2" t="s">
         <v>175</v>
       </c>
@@ -5028,7 +5229,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="30">
+    <row r="40" spans="2:15" ht="31">
       <c r="B40" s="2" t="s">
         <v>189</v>
       </c>
@@ -5121,7 +5322,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="22.5">
+    <row r="50" spans="2:7" ht="24">
       <c r="C50" s="5" t="s">
         <v>203</v>
       </c>
@@ -5151,7 +5352,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="30">
+    <row r="57" spans="2:7" ht="31">
       <c r="B57" s="2" t="s">
         <v>204</v>
       </c>
@@ -5188,7 +5389,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="30">
+    <row r="63" spans="2:7" ht="31">
       <c r="B63" s="2" t="s">
         <v>212</v>
       </c>
@@ -5251,7 +5452,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="2:10" ht="30">
+    <row r="75" spans="2:10" ht="31">
       <c r="B75" s="2" t="s">
         <v>219</v>
       </c>
@@ -5300,7 +5501,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="81" spans="2:13" ht="30">
+    <row r="81" spans="2:13" ht="31">
       <c r="B81" s="2" t="s">
         <v>226</v>
       </c>
@@ -5360,7 +5561,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="88" spans="2:13" ht="30">
+    <row r="88" spans="2:13" ht="31">
       <c r="B88" s="2" t="s">
         <v>239</v>
       </c>
@@ -5397,12 +5598,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="2:13" ht="30">
+    <row r="94" spans="2:13" ht="31">
       <c r="B94" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="95" spans="2:13" ht="22.5">
+    <row r="95" spans="2:13" ht="24">
       <c r="C95" s="5" t="s">
         <v>241</v>
       </c>
@@ -5412,7 +5613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="3:4" ht="22.5">
+    <row r="98" spans="3:4" ht="24">
       <c r="C98" s="5" t="s">
         <v>242</v>
       </c>
@@ -5422,7 +5623,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="3:4" ht="22.5">
+    <row r="101" spans="3:4" ht="24">
       <c r="C101" s="5" t="s">
         <v>244</v>
       </c>
@@ -5482,7 +5683,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="30">
+    <row r="117" spans="2:6" ht="31">
       <c r="B117" s="2" t="s">
         <v>256</v>
       </c>
@@ -5519,7 +5720,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="125" spans="2:6" ht="30">
+    <row r="125" spans="2:6" ht="31">
       <c r="B125" s="2" t="s">
         <v>260</v>
       </c>
@@ -5554,14 +5755,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E9F26F-6ACF-F342-B759-3B01280B6231}">
   <dimension ref="B2:G48"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:4" ht="39.75">
+    <row r="2" spans="2:4" ht="40">
       <c r="B2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="30">
+    <row r="4" spans="2:4" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -5606,7 +5807,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="30">
+    <row r="14" spans="2:4" ht="31">
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
@@ -5684,7 +5885,7 @@
     <row r="30" spans="2:6">
       <c r="C30" s="9"/>
     </row>
-    <row r="31" spans="2:6" ht="30">
+    <row r="31" spans="2:6" ht="31">
       <c r="B31" s="2" t="s">
         <v>110</v>
       </c>
@@ -5721,7 +5922,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="30">
+    <row r="37" spans="2:7" ht="31">
       <c r="B37" s="2" t="s">
         <v>115</v>
       </c>
@@ -5731,7 +5932,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="30">
+    <row r="40" spans="2:7" ht="31">
       <c r="B40" s="2" t="s">
         <v>117</v>
       </c>
@@ -5768,7 +5969,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="30">
+    <row r="46" spans="2:7" ht="31">
       <c r="B46" s="2" t="s">
         <v>121</v>
       </c>
@@ -5793,14 +5994,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E477473-766C-404E-AA4C-BDB1DA1FC5BF}">
   <dimension ref="B2:I45"/>
-  <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="4.28515625" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:3" ht="39.75">
+    <row r="2" spans="2:3" ht="40">
       <c r="B2" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="30">
+    <row r="4" spans="2:3" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -5845,7 +6046,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="30">
+    <row r="17" spans="2:9" ht="31">
       <c r="B17" s="2" t="s">
         <v>127</v>
       </c>
@@ -5945,7 +6146,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="30">
+    <row r="26" spans="2:9" ht="31">
       <c r="B26" s="2" t="s">
         <v>110</v>
       </c>
@@ -5974,7 +6175,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="30">
+    <row r="31" spans="2:9" ht="31">
       <c r="B31" s="2" t="s">
         <v>139</v>
       </c>
@@ -5999,7 +6200,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="30">
+    <row r="37" spans="2:6" ht="31">
       <c r="B37" s="2" t="s">
         <v>117</v>
       </c>
@@ -6033,7 +6234,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="30">
+    <row r="44" spans="2:6" ht="31">
       <c r="B44" s="2" t="s">
         <v>121</v>
       </c>
@@ -6053,14 +6254,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C022DCD-62B0-5943-AD72-B92A39B1DDFD}">
   <dimension ref="B2:K49"/>
-  <sheetFormatPr defaultColWidth="3.44140625" defaultRowHeight="19.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.42578125" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:3" ht="39.75">
+    <row r="2" spans="2:3" ht="40">
       <c r="B2" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="30">
+    <row r="4" spans="2:3" ht="31">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -6105,7 +6306,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="30">
+    <row r="17" spans="2:11" ht="31">
       <c r="B17" s="2" t="s">
         <v>127</v>
       </c>
@@ -6220,7 +6421,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="30">
+    <row r="31" spans="2:11" ht="31">
       <c r="B31" s="2" t="s">
         <v>110</v>
       </c>
@@ -6249,7 +6450,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="30">
+    <row r="36" spans="2:8" ht="31">
       <c r="B36" s="2" t="s">
         <v>139</v>
       </c>
@@ -6274,7 +6475,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="30">
+    <row r="42" spans="2:8" ht="31">
       <c r="B42" s="2" t="s">
         <v>117</v>
       </c>
@@ -6303,7 +6504,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="30">
+    <row r="47" spans="2:8" ht="31">
       <c r="B47" s="2" t="s">
         <v>121</v>
       </c>
